--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487799_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487799_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0177</v>
+        <v>-0.2036</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0041</v>
+        <v>0.1866</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9864</v>
+        <v>-0.3903</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.4683</v>
+        <v>0.7313</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9313</v>
+        <v>-1.3686</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.3996</v>
+        <v>2.0998</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6509</v>
+        <v>2.2339</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7728</v>
+        <v>0.5668</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.1219</v>
+        <v>1.6671</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.1192</v>
+        <v>-1.5027</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8415</v>
+        <v>-1.9354</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2777</v>
+        <v>0.4327</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2487</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3464</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0588</v>
+        <v>0.0339</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4052</v>
+        <v>-0.5525</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8016</v>
+        <v>-0.3899</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3599</v>
+        <v>3.4498</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4418</v>
+        <v>-3.8396</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9648</v>
+        <v>-1.4683</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8954</v>
+        <v>1.9313</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0694</v>
+        <v>-3.3996</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0192</v>
+        <v>1.6509</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0192</v>
+        <v>3.7728</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-2.1219</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9839</v>
+        <v>-3.1192</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9145</v>
+        <v>-1.8415</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0694</v>
+        <v>-1.2777</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2531</v>
+        <v>-0.754</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3791</v>
+        <v>0.5044</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1259</v>
+        <v>-1.2584</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9565</v>
+        <v>-0.7108</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8011</v>
+        <v>-0.1222</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1554</v>
+        <v>-0.5886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7313</v>
+        <v>-0.9648</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3686</v>
+        <v>-0.8954</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0998</v>
+        <v>-0.0694</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2339</v>
+        <v>0.0192</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5668</v>
+        <v>0.0192</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6671</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5027</v>
+        <v>-0.9839</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9354</v>
+        <v>-0.9145</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4327</v>
+        <v>-0.0694</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2715</v>
+        <v>-0.1623</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9539</v>
+        <v>-0.1414</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3176</v>
+        <v>-0.0209</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5811</v>
+        <v>-1.235</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8588</v>
+        <v>0.1056</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7223</v>
+        <v>-1.3406</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3412</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.243</v>
+        <v>-0.8969</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7053</v>
+        <v>0.2591</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5377</v>
+        <v>-1.156</v>
       </c>
       <c r="V6" t="n">
         <v>1.6275</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.706</v>
+        <v>-1.8467</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3124</v>
+        <v>1.9367</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0183</v>
+        <v>-3.7835</v>
       </c>
       <c r="G7" t="n">
         <v>1.4268</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5084</v>
+        <v>-0.6491</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0438</v>
+        <v>0.5806</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4646</v>
+        <v>-1.2297</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1675</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.736</v>
+        <v>-2.2906</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2963</v>
+        <v>-0.9096</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4397</v>
+        <v>-1.381</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6912</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6505</v>
+        <v>-0.205</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>-0.331</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0672</v>
+        <v>0.1259</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3538</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0505</v>
+        <v>-3.6638</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6215</v>
+        <v>-1.2348</v>
       </c>
       <c r="F9" t="n">
         <v>-2.4291</v>
@@ -1156,10 +1156,10 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0124</v>
+        <v>0.3743</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1396</v>
+        <v>0.5263</v>
       </c>
       <c r="U9" t="n">
         <v>-0.152</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8764</v>
+        <v>-9.3714</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1082</v>
+        <v>-6.1628</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7682</v>
+        <v>-3.2086</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1977</v>
@@ -1234,13 +1234,13 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8406</v>
+        <v>0.3456</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1243</v>
+        <v>1.0697</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2837</v>
+        <v>-0.7241</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3975</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.8538</v>
+        <v>-20.8752</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5089</v>
+        <v>-3.5303</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.345</v>
+        <v>-17.3451</v>
       </c>
       <c r="G11" t="n">
         <v>-9.308399999999999</v>
@@ -1312,10 +1312,10 @@
         <v>11.4464</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.5099</v>
+        <v>-2.5312</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4577</v>
+        <v>2.4364</v>
       </c>
       <c r="U11" t="n">
         <v>-4.9677</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.7003</v>
+        <v>11.513</v>
       </c>
       <c r="E12" t="n">
-        <v>9.560499999999999</v>
+        <v>9.8819</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1398</v>
+        <v>1.6311</v>
       </c>
       <c r="G12" t="n">
         <v>6.7741</v>
@@ -1390,13 +1390,13 @@
         <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4475</v>
+        <v>1.2603</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8539</v>
+        <v>1.1754</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4064</v>
+        <v>0.0849</v>
       </c>
       <c r="V12" t="n">
         <v>1.3975</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.054</v>
+        <v>7.42</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9073</v>
+        <v>6.336</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1467</v>
+        <v>1.0841</v>
       </c>
       <c r="G13" t="n">
         <v>5.8208</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>0.152</v>
+        <v>0.518</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2701</v>
+        <v>0.6987</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.118</v>
+        <v>-0.1807</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5838</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7457</v>
+        <v>5.6053</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7064</v>
+        <v>4.5992</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0393</v>
+        <v>1.006</v>
       </c>
       <c r="G14" t="n">
         <v>4.2808</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8207</v>
+        <v>0.6803</v>
       </c>
       <c r="T14" t="n">
-        <v>0.503</v>
+        <v>0.3958</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3178</v>
+        <v>0.2845</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6452</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4304</v>
+        <v>1.0376</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8057</v>
+        <v>-0.8835</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3753</v>
+        <v>1.921</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6</v>
+        <v>-1.4568</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4245</v>
+        <v>1.4285</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1755</v>
+        <v>-2.8853</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1351</v>
+        <v>-1.1178</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3513</v>
+        <v>1.2</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7838000000000001</v>
+        <v>-2.3178</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7351</v>
+        <v>-0.339</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7758</v>
+        <v>0.2284</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9593</v>
+        <v>-0.5674</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>2.0812</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4061</v>
+        <v>0.4131</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9193</v>
+        <v>0.2343</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4868</v>
+        <v>0.1788</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4799</v>
+        <v>0.8748</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6631</v>
+        <v>-0.4299</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1832</v>
+        <v>1.3047</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6617</v>
+        <v>-0.5726</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.403</v>
+        <v>1.2047</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2588</v>
+        <v>-1.7773</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3222</v>
+        <v>-0.1275</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0871</v>
+        <v>1.262</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2351</v>
+        <v>-1.3896</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.984</v>
+        <v>-0.4451</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4901</v>
+        <v>-0.0573</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4939</v>
+        <v>-0.3878</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1218</v>
+        <v>-2.2893</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2893</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9741</v>
+        <v>-0.4714</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2951</v>
+        <v>-0.3481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3209</v>
+        <v>-0.1233</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.455</v>
+        <v>0.0804</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6442</v>
+        <v>0.8413</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0992</v>
+        <v>-0.7609</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5726</v>
+        <v>-0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2047</v>
+        <v>-0.4245</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7773</v>
+        <v>-0.1755</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1275</v>
+        <v>1.1351</v>
       </c>
       <c r="K17" t="n">
-        <v>1.262</v>
+        <v>0.3513</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3896</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4451</v>
+        <v>-1.7351</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0573</v>
+        <v>-0.7758</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3878</v>
+        <v>-0.9593</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2893</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8912</v>
+        <v>1.0561</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5624</v>
+        <v>0.9549</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3288</v>
+        <v>0.1012</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3351</v>
+        <v>-0.5838</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1827</v>
+        <v>-0.2829</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4193</v>
+        <v>-0.3013</v>
       </c>
       <c r="F18" t="n">
-        <v>1.602</v>
+        <v>0.0184</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4568</v>
+        <v>-0.6617</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4285</v>
+        <v>-0.403</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8853</v>
+        <v>-0.2588</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1178</v>
+        <v>0.3222</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2</v>
+        <v>0.0871</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.3178</v>
+        <v>0.2351</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.339</v>
+        <v>-0.984</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2284</v>
+        <v>-0.4901</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5674</v>
+        <v>-0.4939</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0812</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4417</v>
+        <v>1.2113</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3014</v>
+        <v>1.3307</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1402</v>
+        <v>-0.1193</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8247</v>
+        <v>-0.4853</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6977</v>
+        <v>-0.1814</v>
       </c>
       <c r="F19" t="n">
-        <v>0.873</v>
+        <v>-0.3039</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5688</v>
+        <v>-0.9587</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3288</v>
+        <v>0.4815</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.24</v>
+        <v>-1.4402</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0012</v>
+        <v>0.552</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0796</v>
+        <v>1.4982</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0784</v>
+        <v>-0.9463</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5676</v>
+        <v>-1.5106</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2492</v>
+        <v>-1.0167</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3184</v>
+        <v>-0.4939</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8325</v>
+        <v>0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2893</v>
+        <v>-1.2487</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8253</v>
+        <v>0.3308</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8416</v>
+        <v>0.5153</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0163</v>
+        <v>-0.1846</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7513</v>
+        <v>-0.6899</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6616</v>
+        <v>-1.1262</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0386</v>
+        <v>-0.1768</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.623</v>
+        <v>-0.9494</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9587</v>
+        <v>-0.7486</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4815</v>
+        <v>0.2793</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4402</v>
+        <v>-1.0279</v>
       </c>
       <c r="J20" t="n">
-        <v>0.552</v>
+        <v>1.26</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4982</v>
+        <v>1.4347</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9463</v>
+        <v>-0.1747</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5106</v>
+        <v>-2.0086</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0167</v>
+        <v>-1.1554</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4939</v>
+        <v>-0.8532</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.2487</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8455</v>
+        <v>-0.3557</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3419</v>
+        <v>-0.1881</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5036</v>
+        <v>-0.1677</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6899</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6899</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.708</v>
+        <v>-1.3541</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4983</v>
+        <v>-2.3406</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2097</v>
+        <v>0.9865</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7486</v>
+        <v>-2.5688</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2793</v>
+        <v>-2.3288</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0279</v>
+        <v>-0.24</v>
       </c>
       <c r="J21" t="n">
-        <v>1.26</v>
+        <v>-2.0012</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4347</v>
+        <v>-2.0796</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1747</v>
+        <v>0.0784</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0086</v>
+        <v>-0.5676</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1554</v>
+        <v>-0.2492</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8532</v>
+        <v>-0.3184</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R21" t="n">
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9375</v>
+        <v>0.2959</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.1986</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.428</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>1.7513</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>21.8537</v>
+        <v>23.2826</v>
       </c>
       <c r="E22" t="n">
         <v>17.3449</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5088</v>
+        <v>5.937600000000002</v>
       </c>
       <c r="G22" t="n">
-        <v>9.3085</v>
+        <v>9.308499999999999</v>
       </c>
       <c r="H22" t="n">
         <v>9.124700000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1836999999999998</v>
+        <v>0.1837000000000009</v>
       </c>
       <c r="J22" t="n">
         <v>17.0664</v>
@@ -2152,7 +2152,7 @@
         <v>4.245400000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-7.758000000000001</v>
+        <v>-7.758</v>
       </c>
       <c r="N22" t="n">
         <v>-3.6963</v>
@@ -2170,13 +2170,13 @@
         <v>18.7306</v>
       </c>
       <c r="S22" t="n">
-        <v>3.509799999999999</v>
+        <v>4.9387</v>
       </c>
       <c r="T22" t="n">
-        <v>4.967700000000001</v>
+        <v>4.967499999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4576</v>
+        <v>-0.02900000000000007</v>
       </c>
       <c r="V22" t="n">
         <v>1.7512</v>
